--- a/rubika-karnameh/مخاطبین.xlsx
+++ b/rubika-karnameh/مخاطبین.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,10 +33,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00C00000"/>
     </font>
     <font>
       <b val="1"/>
@@ -90,18 +86,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -469,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -479,43 +474,42 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>نام ناحیه</t>
+          <t>نام ناحیه (مثل نام فایل تصویر)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>نام و نام خانوادگی مسئول نسرا (اختیاری)</t>
+          <t>نام در روبیکا — مسئول نسرا (مهم!)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>شماره روبیکای مسئول نسرا</t>
+          <t>شماره موبایل — مسئول نسرا</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>نام و نام خانوادگی فرمانده گردان (اختیاری)</t>
+          <t>نام در روبیکا — فرمانده گردان (مهم!)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>شماره روبیکای فرمانده گردان</t>
+          <t>شماره موبایل — فرمانده گردان</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>نام و نام خانوادگی مسئول فضای مجازی (اختیاری)</t>
+          <t>نام در روبیکا — مسئول فضای مجازی (مهم!)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>شماره روبیکای مسئول فضای مجازی</t>
+          <t>شماره موبایل — مسئول فضای مجازی</t>
         </is>
       </c>
     </row>
@@ -531,11 +525,6 @@
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>⟵ برای تست، شماره‌ی موبایل خودتان را در ستون «شماره روبیکای مسئول نسرا» بنویسید</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -548,98 +537,123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>📖 راهنمای فایل مخاطبین</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr"/>
+      <c r="A2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>هر سطرِ این جدول یک ناحیه است. نام ناحیه باید دقیقاً مثل نام فایل تصویر باشد؛</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>✔ ستون «نام در روبیکا» مهم‌ترین ستون است: نام هر مسئول را</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>یعنی اگر تصویرِ ناحیه «کارنامه_ناحیه ۴.png» باشد، در ستون اول باید بنویسید: ناحیه ۴</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    همان‌طور که در لیست گفتگوهای روبیکای خودتان می‌بینید بنویسید؛</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr"/>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ارسال با جستجوی همین نام انجام می‌شود.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>✅ ستون‌های «شماره روبیکا» را با شماره‌ی موبایلِ هر مسئول پر کنید.</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>✔ فقط کسانی که قبلاً با آن‌ها گفتگو داشته‌اید پیدا می‌شوند؛</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>✅ ستون‌های «نام و نام خانوادگی» اختیاری‌اند؛ فقط برای یادداشتِ خودتان است.</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    برای بقیه یک بار از گوشی بهشان پیام بدهید تا گفتگو ساخته شود.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>✅ شماره را هر شکلی بنویسید (۰۹۱۲… یا +۹۸۹۱۲… یا با خط تیره)؛ خودش درست می‌خواند.</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>✔ شماره موبایل را هم بنویسید (برای شناسایی و پشتیبانی).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>✅ اگر یک نفر دو نقش دارد، همان یک شماره را دوبار بنویسید؛ فقط یک پیام می‌گیرد.</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>✔ نام ناحیه (ستون اول) باید دقیقاً مثل نام فایل تصویر باشد:</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>✅ ناحیه‌ای که شماره‌ای ندارد، رد می‌شود (خطا نمی‌دهد).</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    تصویر «کارنامه_ناحیه ۴.png» ← در اکسل بنویسید: ناحیه ۴</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>✔ شماره را هر شکلی بنویسید (۰۹۱۲… یا +۹۸۹۱۲…)؛ خودش درست می‌خواند.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>🧪 برای تست: در ردیف «ناحیه تست»، شماره‌ی موبایل خودتان را در ستون شماره‌ی</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>✔ اگر یک نفر دو نقش دارد، همان یک شماره را دوبار بنویسید؛ یک پیام می‌گیرد.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    مسئول نسرا بنویسید و فایل 2-تست-به-خودم.bat را اجرا کنید.</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>✔ ناحیه‌ای که نام یا شماره ندارد، رد می‌شود (خطا نمی‌دهد).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr"/>
+      <c r="A14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>⚠️ قبل از اجرای ارسال، این فایل را ذخیره کنید و ببندید (اکسل نباید باز باشد).</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>🧪 برای تست: در ردیف «ناحیه تست»، نام و شماره‌ی کسی که گفتگو دارید</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (یا خودتان) را بنویسید و فایل 2-تست-به-خودم.bat را اجرا کنید.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>⚠️ قبل از اجرای ارسال، این فایل را ذخیره کنید و ببندید.</t>
         </is>
       </c>
     </row>

--- a/rubika-karnameh/مخاطبین.xlsx
+++ b/rubika-karnameh/مخاطبین.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -474,6 +474,10 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -484,32 +488,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>نام در روبیکا — مسئول نسرا (مهم!)</t>
+          <t>نام در روبیکا — مسئولین فضای مجازی (مهم!)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>شماره موبایل — مسئول نسرا</t>
+          <t>شماره موبایل — مسئولین فضای مجازی</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>نام در روبیکا — فرمانده گردان (مهم!)</t>
+          <t>نام در روبیکا — فرمانده گردان خواهر (مهم!)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>شماره موبایل — فرمانده گردان</t>
+          <t>شماره موبایل — فرمانده گردان خواهر</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>نام در روبیکا — مسئول فضای مجازی (مهم!)</t>
+          <t>نام در روبیکا — فرمانده گردان برادر (مهم!)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>شماره موبایل — مسئول فضای مجازی</t>
+          <t>شماره موبایل — فرمانده گردان برادر</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>نام در روبیکا — مسئول نسرا خواهر (مهم!)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>شماره موبایل — مسئول نسرا خواهر</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>نام در روبیکا — مسئول نسرا برادر (مهم!)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>شماره موبایل — مسئول نسرا برادر</t>
         </is>
       </c>
     </row>
@@ -525,6 +549,10 @@
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -537,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -653,6 +681,37 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>🗂 دسته‌های ارسال: مسئولین فضای مجازی، فرمانده گردان خواهر،</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    فرمانده گردان برادر، مسئول نسرا خواهر، مسئول نسرا برادر.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>✔ هنگام اجرای فایل ارسال/لیست، از شما پرسیده می‌شود کدام دسته‌ها؛</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    شماره‌ها را بنویسید (مثلاً 4 5) یا 0 برای همه‌ی دسته‌ها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>⚠️ قبل از اجرای ارسال، این فایل را ذخیره کنید و ببندید.</t>
         </is>
       </c>
